--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486281_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486281_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7093</v>
+        <v>6.666</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0307</v>
+        <v>3.9874</v>
       </c>
       <c r="F2" t="n">
         <v>2.6786</v>
@@ -610,10 +610,10 @@
         <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.435</v>
+        <v>-0.4783</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3389</v>
+        <v>-0.3821</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0961</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4725</v>
+        <v>3.1596</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6443</v>
+        <v>1.8245</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8282</v>
+        <v>1.3351</v>
       </c>
       <c r="G3" t="n">
         <v>1.0242</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0786</v>
+        <v>-0.2343</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9469</v>
+        <v>-0.7667</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0255</v>
+        <v>0.5323</v>
       </c>
       <c r="V3" t="n">
         <v>1.4997</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3007</v>
+        <v>1.9049</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1418</v>
+        <v>-0.578</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4425</v>
+        <v>2.4828</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4495</v>
+        <v>1.9044</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1069</v>
+        <v>0.8972</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3426</v>
+        <v>1.0072</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2549</v>
+        <v>1.0535</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5896</v>
+        <v>0.9006</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6653</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1946</v>
+        <v>0.8509</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5173</v>
+        <v>-0.0033</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3227</v>
+        <v>0.8542</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1751</v>
+        <v>-0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2626</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7501</v>
+        <v>-0.4993</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6802</v>
+        <v>-0.5864</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.4303</v>
+        <v>0.0871</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3252</v>
+        <v>0.9347</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>-0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1813</v>
+        <v>0.8767</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.87</v>
+        <v>-0.8124</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0513</v>
+        <v>1.6891</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9044</v>
+        <v>-1.4495</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8972</v>
+        <v>-1.1069</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0072</v>
+        <v>-0.3426</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0535</v>
+        <v>-1.2549</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9006</v>
+        <v>-0.5896</v>
       </c>
       <c r="L5" t="n">
-        <v>0.153</v>
+        <v>-0.6653</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8509</v>
+        <v>-0.1946</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0033</v>
+        <v>-0.5173</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8542</v>
+        <v>0.3227</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>3.2626</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2228</v>
+        <v>-1.1741</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8784</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3444</v>
+        <v>-1.1837</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9347</v>
+        <v>1.3252</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.5204</v>
       </c>
       <c r="X5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0013</v>
+        <v>0.5784</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4217</v>
+        <v>-1.9062</v>
       </c>
       <c r="F6" t="n">
-        <v>2.423</v>
+        <v>2.4847</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1963</v>
@@ -922,13 +922,13 @@
         <v>3.2626</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.735</v>
+        <v>-1.1578</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5754</v>
+        <v>-1.0599</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1596</v>
+        <v>-0.098</v>
       </c>
       <c r="V6" t="n">
         <v>3.0202</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2941</v>
+        <v>-0.244</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1083</v>
+        <v>-0.9966</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8143</v>
+        <v>0.7526</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3622</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4317</v>
+        <v>-0.3815</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0478</v>
+        <v>-0.0138</v>
       </c>
       <c r="V7" t="n">
         <v>0.9347</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.496</v>
+        <v>-0.5422</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3269</v>
+        <v>-1.8799</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8309</v>
+        <v>1.3377</v>
       </c>
       <c r="G9" t="n">
         <v>0.4901</v>
@@ -1156,13 +1156,13 @@
         <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7914</v>
+        <v>-0.8376</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3064</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.038</v>
+        <v>-0.5312</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4997</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7357</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2051</v>
+        <v>0.2736</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9408</v>
+        <v>-0.8175</v>
       </c>
       <c r="G10" t="n">
         <v>2.7185</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6939</v>
+        <v>-1.5021</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4795</v>
+        <v>-0.411</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2144</v>
+        <v>-1.0911</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0835</v>
+        <v>-1.1027</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5111</v>
+        <v>-1.6229</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4276</v>
+        <v>0.5201</v>
       </c>
       <c r="G11" t="n">
         <v>0.3171</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1422</v>
+        <v>0.1229</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4831</v>
+        <v>0.3713</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3409</v>
+        <v>-0.2485</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3252</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1795</v>
+        <v>-1.534</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3433</v>
+        <v>-2.7904</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1639</v>
+        <v>1.2563</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3081</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1318</v>
+        <v>-0.4864</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3509</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2191</v>
+        <v>0.3115</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7395</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.502299999999998</v>
+        <v>8.844800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7306</v>
+        <v>-4.388500000000001</v>
       </c>
       <c r="F13" t="n">
         <v>13.2331</v>
@@ -1468,13 +1468,13 @@
         <v>21.7508</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.5105</v>
+        <v>-7.168100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.776699999999999</v>
+        <v>-4.4342</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.7339</v>
+        <v>-2.7341</v>
       </c>
       <c r="V13" t="n">
         <v>2.0647</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4915</v>
+        <v>3.7194</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2022</v>
+        <v>3.9728</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7107</v>
+        <v>-0.2535</v>
       </c>
       <c r="G14" t="n">
         <v>2.4088</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9972</v>
+        <v>1.2251</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7473</v>
+        <v>0.5179</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2499</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.9554</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1272</v>
+        <v>-0.0332</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3288</v>
+        <v>-1.1419</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2017</v>
+        <v>1.1087</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7971</v>
+        <v>-2.3476</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2441</v>
+        <v>-1.4631</v>
       </c>
       <c r="I15" t="n">
-        <v>0.447</v>
+        <v>-0.8845</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5244</v>
+        <v>-0.4285</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5443</v>
+        <v>-0.4134</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0199</v>
+        <v>-0.0151</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2727</v>
+        <v>-1.9191</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6998</v>
+        <v>-1.0497</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4271</v>
+        <v>-0.8694</v>
       </c>
       <c r="P15" t="n">
-        <v>2.8276</v>
+        <v>1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="R15" t="n">
-        <v>3.0451</v>
+        <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9216</v>
+        <v>0.4873</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0707</v>
+        <v>-0.3208</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1491</v>
+        <v>0.8081</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.8249</v>
+        <v>0.7395</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.8249</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0732</v>
+        <v>-0.2814</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9762</v>
+        <v>-2.4232</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0493</v>
+        <v>2.1418</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4455</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3463</v>
+        <v>0.9917</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0227</v>
+        <v>0.5756</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3236</v>
+        <v>0.4161</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0376</v>
+        <v>-0.3777</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1618</v>
+        <v>-0.4535</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1242</v>
+        <v>0.0757</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1314</v>
+        <v>-0.7971</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0216</v>
+        <v>-1.2441</v>
       </c>
       <c r="I17" t="n">
-        <v>0.153</v>
+        <v>0.447</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8671</v>
+        <v>-0.5244</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1642</v>
+        <v>-0.5443</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7029</v>
+        <v>0.0199</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7357</v>
+        <v>-0.2727</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1858</v>
+        <v>-0.6998</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5499</v>
+        <v>0.4271</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.87</v>
+        <v>2.8276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>3.0451</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9061</v>
+        <v>0.4167</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8172</v>
+        <v>0.2884</v>
       </c>
       <c r="U17" t="n">
-        <v>1.089</v>
+        <v>0.1283</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.13</v>
+        <v>-2.8249</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1149</v>
+        <v>-0.5918</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2595</v>
+        <v>0.9382</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1446</v>
+        <v>-1.53</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3476</v>
+        <v>0.1314</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4631</v>
+        <v>-0.0216</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8845</v>
+        <v>0.153</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4285</v>
+        <v>1.8671</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4134</v>
+        <v>0.1642</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0151</v>
+        <v>1.7029</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9191</v>
+        <v>-1.7357</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0497</v>
+        <v>-0.1858</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8694</v>
+        <v>-1.5499</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>-0.87</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.5225</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6101</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5944</v>
+        <v>1.2768</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4384</v>
+        <v>0.5936</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8441</v>
+        <v>0.6832</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6212</v>
+        <v>-1.2112</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4767</v>
+        <v>-2.6019</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8555</v>
+        <v>1.3907</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4602</v>
+        <v>2.3757</v>
       </c>
       <c r="H19" t="n">
-        <v>0.359</v>
+        <v>1.0434</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8192</v>
+        <v>1.3324</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3766</v>
+        <v>2.9975</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2618</v>
+        <v>1.5607</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>1.4368</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8368</v>
+        <v>-0.6217</v>
       </c>
       <c r="N19" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.5173</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9339</v>
+        <v>-0.1044</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.6101</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.5676</v>
+        <v>-5.4377</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8189</v>
+        <v>0.6757</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9542</v>
+        <v>-0.3569</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8647</v>
+        <v>1.0325</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7276</v>
+        <v>-1.8292</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2724</v>
+        <v>-4.1596</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5448</v>
+        <v>2.3304</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3757</v>
+        <v>-3.9056</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0434</v>
+        <v>-0.7724</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3324</v>
+        <v>-3.1332</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9975</v>
+        <v>-1.9514</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5607</v>
+        <v>-0.0056</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4368</v>
+        <v>-1.9459</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6217</v>
+        <v>-1.9541</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5173</v>
+        <v>-0.7668</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1044</v>
+        <v>-1.1873</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.6976</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.4377</v>
+        <v>-2.6101</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>3.2626</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1592</v>
+        <v>0.4891</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0274</v>
+        <v>0.2067</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1867</v>
+        <v>0.2824</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.9347</v>
       </c>
       <c r="W20" t="n">
         <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7602</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9127</v>
+        <v>-2.0798</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.7242</v>
+        <v>-2.812</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8115</v>
+        <v>0.7322</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.9056</v>
+        <v>-0.4602</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7724</v>
+        <v>0.359</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1332</v>
+        <v>-0.8192</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9514</v>
+        <v>0.3766</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0056</v>
+        <v>0.2618</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9459</v>
+        <v>0.1147</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9541</v>
+        <v>-0.8368</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7668</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1873</v>
+        <v>-0.9339</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.6101</v>
+        <v>-4.5676</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2626</v>
+        <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5944</v>
+        <v>1.3603</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3579</v>
+        <v>0.6189</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2365</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9347</v>
+        <v>-0.3698</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8553</v>
+        <v>-5.0724</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2169</v>
+        <v>-4.5522</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6385</v>
+        <v>-0.5203</v>
       </c>
       <c r="G22" t="n">
         <v>-6.5582</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5501</v>
+        <v>1.333</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9458</v>
+        <v>0.6105</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.7225</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9347</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.502199999999998</v>
+        <v>-7.7573</v>
       </c>
       <c r="E23" t="n">
-        <v>-13.2331</v>
+        <v>-13.2333</v>
       </c>
       <c r="F23" t="n">
-        <v>4.730600000000001</v>
+        <v>5.4757</v>
       </c>
       <c r="G23" t="n">
         <v>-9.5983</v>
@@ -2218,7 +2218,7 @@
         <v>-1.8249</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.7733</v>
+        <v>-7.773299999999999</v>
       </c>
       <c r="J23" t="n">
         <v>1.7666</v>
@@ -2227,7 +2227,7 @@
         <v>3.1807</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4143</v>
+        <v>-1.414299999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-11.3648</v>
@@ -2239,7 +2239,7 @@
         <v>-6.359</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.350200000000001</v>
+        <v>-4.350199999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-21.7506</v>
@@ -2248,13 +2248,13 @@
         <v>17.4005</v>
       </c>
       <c r="S23" t="n">
-        <v>7.5106</v>
+        <v>8.255699999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7342</v>
+        <v>2.7339</v>
       </c>
       <c r="U23" t="n">
-        <v>4.7767</v>
+        <v>5.521700000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0648</v>
